--- a/data/trans_dic/CAGE_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/CAGE_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE)</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -722,37 +722,37 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,56</t>
+          <t>0,87; 3,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 3,12</t>
+          <t>0,25; 3,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,8</t>
+          <t>0,97; 4,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,26</t>
+          <t>0,27; 3,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,72</t>
+          <t>0,32; 3,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,23</t>
+          <t>0,42; 2,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,29</t>
+          <t>0,48; 2,37</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,29</t>
+          <t>0,9; 3,39</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 4,16</t>
+          <t>0,24; 3,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,5</t>
+          <t>0,24; 2,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,69</t>
+          <t>0,08; 2,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,42</t>
+          <t>0,25; 2,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,84</t>
+          <t>0,64; 4,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,24</t>
+          <t>0,13; 1,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,36</t>
+          <t>0,29; 2,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,7</t>
+          <t>0,35; 1,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,77</t>
+          <t>0,59; 2,74</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,95</t>
+          <t>0,31; 1,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,47</t>
+          <t>0,98; 3,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,12</t>
+          <t>0,77; 3,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 6,04</t>
+          <t>0,89; 5,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,4</t>
+          <t>0,0; 4,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,43</t>
+          <t>0,25; 1,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,52</t>
+          <t>0,66; 2,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,75</t>
+          <t>0,81; 2,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,97</t>
+          <t>0,99; 5,34</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,71</t>
+          <t>0,58; 1,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,08</t>
+          <t>1,29; 2,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,4</t>
+          <t>0,85; 2,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 5,01</t>
+          <t>1,46; 4,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,97</t>
+          <t>0,1; 1,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,34</t>
+          <t>0,45; 1,3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,81</t>
+          <t>0,81; 1,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,56</t>
+          <t>0,62; 1,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,97</t>
+          <t>0,66; 3,08</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,66</t>
+          <t>0,28; 2,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,3</t>
+          <t>0,91; 3,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,67</t>
+          <t>0,62; 2,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,8</t>
+          <t>1,52; 6,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,01</t>
+          <t>0,18; 1,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,9</t>
+          <t>0,75; 4,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,67</t>
+          <t>0,35; 1,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,54</t>
+          <t>0,5; 1,54</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,37</t>
+          <t>0,37; 1,37</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,7</t>
+          <t>1,72; 4,82</t>
         </is>
       </c>
     </row>
@@ -1417,27 +1417,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,45</t>
+          <t>1,1; 4,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,4</t>
+          <t>0,97; 4,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,44</t>
+          <t>0,0; 0,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,41</t>
+          <t>0,0; 9,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,11</t>
+          <t>0,28; 1,11</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,21</t>
+          <t>0,35; 1,23</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,18</t>
+          <t>0,0; 4,88</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,15</t>
+          <t>0,53; 1,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,5</t>
+          <t>1,46; 2,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,09; 1,94</t>
+          <t>1,05; 1,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,23</t>
+          <t>1,59; 3,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,53</t>
+          <t>0,12; 0,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,32</t>
+          <t>0,06; 0,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,8</t>
+          <t>0,28; 0,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,03</t>
+          <t>0,54; 2,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,74</t>
+          <t>0,37; 0,73</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,3</t>
+          <t>0,78; 1,31</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,24</t>
+          <t>0,73; 1,22</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,55</t>
+          <t>1,27; 2,52</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE)</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4671</t>
+          <t>0; 4706</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3710; 15568</t>
+          <t>3790; 16261</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1085; 13390</t>
+          <t>1064; 13288</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3053; 13448</t>
+          <t>2718; 12375</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5643</t>
+          <t>0; 4932</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2125</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>924; 11301</t>
+          <t>924; 12043</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>503; 5887</t>
+          <t>509; 6142</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5890</t>
+          <t>0; 5881</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3691; 16735</t>
+          <t>3147; 16915</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3739; 17800</t>
+          <t>3732; 18378</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4230; 14399</t>
+          <t>3962; 14870</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7389</t>
+          <t>0; 7813</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>985; 17436</t>
+          <t>990; 15859</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>935; 9416</t>
+          <t>916; 8646</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>169; 5691</t>
+          <t>167; 6003</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4875</t>
+          <t>0; 5122</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5713</t>
+          <t>0; 6377</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>940; 9019</t>
+          <t>942; 9098</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>880; 6368</t>
+          <t>839; 6533</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>970; 9133</t>
+          <t>963; 8160</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2119; 17878</t>
+          <t>2163; 17564</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2187; 12770</t>
+          <t>2623; 13578</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2039; 9494</t>
+          <t>2042; 9425</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1724; 10550</t>
+          <t>1702; 10220</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5789; 21855</t>
+          <t>6196; 23159</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4144; 16296</t>
+          <t>3999; 16999</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2344; 12759</t>
+          <t>1885; 11373</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1951</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2038</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 7317</t>
+          <t>0; 7091</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 1119</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1683; 10127</t>
+          <t>1771; 10262</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5738; 22419</t>
+          <t>5857; 22743</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5337; 18900</t>
+          <t>5573; 19921</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2425; 12507</t>
+          <t>2502; 13442</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6696; 21131</t>
+          <t>7200; 22125</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15373; 35703</t>
+          <t>14943; 34253</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10118; 27645</t>
+          <t>9727; 27887</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7037; 25451</t>
+          <t>7438; 25327</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 9187</t>
+          <t>0; 8266</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4978</t>
+          <t>0; 6013</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>823; 8004</t>
+          <t>826; 8303</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 6238</t>
+          <t>0; 6158</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8866; 26138</t>
+          <t>8811; 25315</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14787; 34787</t>
+          <t>15585; 36043</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11676; 30848</t>
+          <t>12298; 32211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6007; 27368</t>
+          <t>6087; 28374</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>921; 9323</t>
+          <t>972; 9000</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4763; 16849</t>
+          <t>4623; 16764</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4113; 16544</t>
+          <t>3852; 16808</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3689; 13400</t>
+          <t>3513; 14406</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1014; 11441</t>
+          <t>1018; 9998</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6078</t>
+          <t>0; 7156</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5498</t>
+          <t>0; 6382</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1030; 6424</t>
+          <t>981; 6233</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3013; 15396</t>
+          <t>3255; 15010</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5771; 19531</t>
+          <t>6371; 19606</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4917; 18623</t>
+          <t>4988; 18559</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5515; 17033</t>
+          <t>6245; 17475</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5300</t>
+          <t>0; 5414</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3005; 14549</t>
+          <t>2947; 13224</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2040; 12635</t>
+          <t>2788; 13169</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 4530</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 5502</t>
+          <t>0; 5117</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4942</t>
+          <t>0; 4954</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>946; 9703</t>
+          <t>951; 9752</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 11422</t>
+          <t>0; 11404</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 6305</t>
+          <t>0; 6289</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3308; 15303</t>
+          <t>3873; 15209</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4764; 16615</t>
+          <t>4736; 16829</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 11196</t>
+          <t>0; 10555</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16580; 37591</t>
+          <t>17416; 38326</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>49913; 85396</t>
+          <t>50049; 86151</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36763; 65792</t>
+          <t>35386; 64007</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24874; 49692</t>
+          <t>24448; 47807</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3974; 17949</t>
+          <t>3917; 17683</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1994; 11408</t>
+          <t>1991; 11105</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10035; 28290</t>
+          <t>9738; 26091</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5270; 20140</t>
+          <t>5372; 20155</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>25151; 49074</t>
+          <t>24613; 48851</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>53641; 90875</t>
+          <t>54487; 91002</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51664; 85504</t>
+          <t>50640; 84500</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>33218; 64544</t>
+          <t>32081; 63736</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/CAGE_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/CAGE_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -722,22 +722,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,72</t>
+          <t>0,85; 3,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 3,1</t>
+          <t>0,25; 3,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,42</t>
+          <t>1,29; 5,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,47</t>
+          <t>0,27; 3,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,88</t>
+          <t>0,31; 3,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,75</t>
+          <t>0,0; 0,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,25</t>
+          <t>0,49; 2,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,37</t>
+          <t>0,48; 2,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,39</t>
+          <t>1,1; 3,8</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,79</t>
+          <t>0,23; 4,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,29</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,84</t>
+          <t>0,31; 3,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,44</t>
+          <t>0,25; 2,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,96</t>
+          <t>0,98; 5,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,1</t>
+          <t>0,13; 1,12</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,32</t>
+          <t>0,28; 2,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,81</t>
+          <t>0,28; 1,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,74</t>
+          <t>0,84; 3,24</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,88</t>
+          <t>0,32; 1,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,68</t>
+          <t>0,92; 3,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,26</t>
+          <t>0,79; 3,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,38</t>
+          <t>1,43; 7,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,27</t>
+          <t>0,0; 3,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,22 +1037,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,44</t>
+          <t>0,23; 1,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,56</t>
+          <t>0,67; 2,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,9</t>
+          <t>0,75; 2,73</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,34</t>
+          <t>1,14; 5,79</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,79</t>
+          <t>0,58; 1,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,96</t>
+          <t>1,29; 2,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,43</t>
+          <t>0,85; 2,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,98</t>
+          <t>1,26; 4,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,16</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,01</t>
+          <t>0,1; 0,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,45; 5,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,3</t>
+          <t>0,47; 1,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,87</t>
+          <t>0,82; 1,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,63</t>
+          <t>0,62; 1,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,08</t>
+          <t>1,33; 3,73</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,57</t>
+          <t>0,26; 2,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,28</t>
+          <t>0,91; 3,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,71</t>
+          <t>0,66; 2,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,23</t>
+          <t>1,66; 6,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,76</t>
+          <t>0,18; 1,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,86</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,75</t>
+          <t>0,77; 4,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,63</t>
+          <t>0,4; 1,68</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,54</t>
+          <t>0,46; 1,53</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,37</t>
+          <t>0,36; 1,4</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,82</t>
+          <t>1,64; 4,69</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -1417,17 +1417,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,82</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,96</t>
+          <t>1,11; 5,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,59</t>
+          <t>0,96; 4,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,41</t>
+          <t>0,0; 0,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,45</t>
+          <t>0,0; 0,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,9</t>
+          <t>0,1; 0,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,39</t>
+          <t>0,0; 9,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,41</t>
+          <t>0,0; 0,47</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,11</t>
+          <t>0,27; 1,11</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,23</t>
+          <t>0,35; 1,29</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,88</t>
+          <t>0,0; 5,31</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,17</t>
+          <t>0,5; 1,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,52</t>
+          <t>1,46; 2,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,89</t>
+          <t>1,05; 1,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,11</t>
+          <t>1,73; 3,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,52</t>
+          <t>0,12; 0,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,31</t>
+          <t>0,06; 0,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,74</t>
+          <t>0,28; 0,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,03</t>
+          <t>1,02; 3,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,73</t>
+          <t>0,38; 0,74</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,31</t>
+          <t>0,76; 1,29</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,22</t>
+          <t>0,73; 1,23</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,52</t>
+          <t>1,67; 2,9</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8294</t>
+          <t>10448</t>
         </is>
       </c>
     </row>
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4706</t>
+          <t>0; 4711</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3790; 16261</t>
+          <t>3713; 16080</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1064; 13288</t>
+          <t>1066; 13725</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2718; 12375</t>
+          <t>3898; 15987</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4932</t>
+          <t>0; 4584</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1957,32 +1957,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>924; 12043</t>
+          <t>932; 11908</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>509; 6142</t>
+          <t>536; 5613</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5881</t>
+          <t>0; 6884</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3147; 16915</t>
+          <t>3713; 17209</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3732; 18378</t>
+          <t>3694; 17420</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3962; 14870</t>
+          <t>5185; 17909</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>2574</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>6203</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7813</t>
+          <t>0; 7312</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>990; 15859</t>
+          <t>983; 17363</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>916; 8646</t>
+          <t>0; 8641</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>167; 6003</t>
+          <t>683; 7289</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5122</t>
+          <t>0; 5218</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6377</t>
+          <t>0; 5768</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>942; 9098</t>
+          <t>939; 8537</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>839; 6533</t>
+          <t>1407; 8152</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>963; 8160</t>
+          <t>960; 8284</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2163; 17564</t>
+          <t>2122; 18690</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2623; 13578</t>
+          <t>2084; 13133</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2042; 9425</t>
+          <t>3061; 11865</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>7946</t>
         </is>
       </c>
     </row>
@@ -2343,22 +2343,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1702; 10220</t>
+          <t>1712; 10143</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6196; 23159</t>
+          <t>5795; 22589</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3999; 16999</t>
+          <t>4115; 16816</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1885; 11373</t>
+          <t>3260; 17156</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 7091</t>
+          <t>0; 6487</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2383,22 +2383,22 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1771; 10262</t>
+          <t>1623; 9992</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5857; 22743</t>
+          <t>5961; 24407</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5573; 19921</t>
+          <t>5135; 18762</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2502; 13442</t>
+          <t>3119; 15907</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13791</t>
+          <t>12615</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15817</t>
+          <t>16783</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7200; 22125</t>
+          <t>7184; 22053</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14943; 34253</t>
+          <t>15008; 34599</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9727; 27887</t>
+          <t>9799; 27550</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7438; 25327</t>
+          <t>6821; 21815</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 8266</t>
+          <t>0; 8970</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6013</t>
+          <t>0; 5687</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>826; 8303</t>
+          <t>815; 7690</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 6158</t>
+          <t>1033; 13120</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8811; 25315</t>
+          <t>9222; 26260</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15585; 36043</t>
+          <t>15793; 36253</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12298; 32211</t>
+          <t>12187; 31686</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6087; 28374</t>
+          <t>10175; 28604</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>8758</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>11688</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>972; 9000</t>
+          <t>911; 9524</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4623; 16764</t>
+          <t>4626; 16343</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3852; 16808</t>
+          <t>4118; 17811</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3513; 14406</t>
+          <t>4267; 15939</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1018; 9998</t>
+          <t>1027; 10490</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 7156</t>
+          <t>0; 7052</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6382</t>
+          <t>0; 6127</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>981; 6233</t>
+          <t>1187; 6490</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3255; 15010</t>
+          <t>3644; 15485</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6371; 19606</t>
+          <t>5885; 19466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4988; 18559</t>
+          <t>4931; 18970</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6245; 17475</t>
+          <t>6737; 19261</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
     </row>
@@ -2967,17 +2967,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5414</t>
+          <t>0; 6440</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2947; 13224</t>
+          <t>2965; 14205</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2788; 13169</t>
+          <t>2751; 12016</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 5117</t>
+          <t>0; 5385</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4954</t>
+          <t>0; 5462</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>951; 9752</t>
+          <t>1064; 9551</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 11404</t>
+          <t>0; 11629</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 6289</t>
+          <t>0; 7347</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3873; 15209</t>
+          <t>3753; 15238</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4736; 16829</t>
+          <t>4844; 17652</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 10555</t>
+          <t>0; 11279</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35145</t>
+          <t>40337</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>11749</t>
+          <t>14955</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>46894</t>
+          <t>55293</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>17416; 38326</t>
+          <t>16198; 37731</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>50049; 86151</t>
+          <t>50083; 84144</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35386; 64007</t>
+          <t>35537; 63606</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24448; 47807</t>
+          <t>28319; 55684</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3917; 17683</t>
+          <t>4152; 18144</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1991; 11105</t>
+          <t>1992; 11274</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9738; 26091</t>
+          <t>10026; 27187</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5372; 20155</t>
+          <t>8841; 26976</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>24613; 48851</t>
+          <t>25307; 49437</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>54487; 91002</t>
+          <t>53311; 90202</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>50640; 84500</t>
+          <t>50366; 85033</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>32081; 63736</t>
+          <t>41851; 72607</t>
         </is>
       </c>
     </row>
